--- a/WorkBot/main/data/orders/Ithaca Bakery/Ithaca Bakery_Triphammer_20260529.xlsx
+++ b/WorkBot/main/data/orders/Ithaca Bakery/Ithaca Bakery_Triphammer_20260529.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1356,6 +1356,65 @@
         <v>0</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Container - HD Deli (32oz)</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>72.98999999999999</v>
+      </c>
+      <c r="E51" t="n">
+        <v>72.98999999999999</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Floor Cleaner - Lucky 7</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="E52" t="n">
+        <v>12.55</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>H&amp;M/JP</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Scrubbies - Steel</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="E53" t="n">
+        <v>8.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
